--- a/output_data.xlsx
+++ b/output_data.xlsx
@@ -831,10 +831,10 @@
         <v>299</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>72.35071659088135</v>
+        <v>0.4567988682538271</v>
       </c>
     </row>
     <row r="18">
@@ -969,10 +969,10 @@
         <v>301</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>79.23816442489624</v>
+        <v>3.82302813231945</v>
       </c>
     </row>
     <row r="24">
@@ -1935,10 +1935,10 @@
         <v>299</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>72.0207154750824</v>
+        <v>0.7760573644191027</v>
       </c>
     </row>
     <row r="66">
@@ -2280,10 +2280,10 @@
         <v>301</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>80.88147640228271</v>
+        <v>5.199091136455536</v>
       </c>
     </row>
     <row r="81">
@@ -2441,10 +2441,10 @@
         <v>303</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>78.52189540863037</v>
+        <v>2.554357424378395</v>
       </c>
     </row>
     <row r="88">
@@ -2464,10 +2464,10 @@
         <v>316</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>87.95656561851501</v>
+        <v>11.03186681866646</v>
       </c>
     </row>
     <row r="89">
@@ -2648,10 +2648,10 @@
         <v>306</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>79.74337339401245</v>
+        <v>5.080516636371613</v>
       </c>
     </row>
     <row r="97">
@@ -2832,10 +2832,10 @@
         <v>314</v>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>87.24761009216309</v>
+        <v>10.47729477286339</v>
       </c>
     </row>
     <row r="105">
@@ -3016,10 +3016,10 @@
         <v>308</v>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>74.73152875900269</v>
+        <v>1.768307201564312</v>
       </c>
     </row>
     <row r="113">
@@ -3039,10 +3039,10 @@
         <v>307</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>85.37964820861816</v>
+        <v>7.988868653774261</v>
       </c>
     </row>
     <row r="114">
@@ -3177,10 +3177,10 @@
         <v>301</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>75.19436478614807</v>
+        <v>1.640664413571358</v>
       </c>
     </row>
     <row r="120">
@@ -3522,10 +3522,10 @@
         <v>318</v>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>80.90943694114685</v>
+        <v>6.006587296724319</v>
       </c>
     </row>
     <row r="135">
@@ -3614,10 +3614,10 @@
         <v>307</v>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>80.00828623771667</v>
+        <v>4.915879666805267</v>
       </c>
     </row>
     <row r="139">
@@ -3913,10 +3913,10 @@
         <v>315</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>83.06225538253784</v>
+        <v>7.958333194255829</v>
       </c>
     </row>
     <row r="152">
@@ -5017,10 +5017,10 @@
         <v>307</v>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G199" t="n">
-        <v>76.9827127456665</v>
+        <v>3.143205493688583</v>
       </c>
     </row>
     <row r="200">
@@ -5155,10 +5155,10 @@
         <v>308</v>
       </c>
       <c r="F205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>74.18232560157776</v>
+        <v>1.565248146653175</v>
       </c>
     </row>
     <row r="206">
@@ -5178,10 +5178,10 @@
         <v>319</v>
       </c>
       <c r="F206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G206" t="n">
-        <v>77.44934558868408</v>
+        <v>5.26919886469841</v>
       </c>
     </row>
     <row r="207">
@@ -5822,10 +5822,10 @@
         <v>311</v>
       </c>
       <c r="F234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>75.37994980812073</v>
+        <v>2.670826949179173</v>
       </c>
     </row>
     <row r="235">
@@ -5845,10 +5845,10 @@
         <v>303</v>
       </c>
       <c r="F235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G235" t="n">
-        <v>77.61995792388916</v>
+        <v>3.226479142904282</v>
       </c>
     </row>
     <row r="236">
@@ -6098,10 +6098,10 @@
         <v>312</v>
       </c>
       <c r="F246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G246" t="n">
-        <v>81.38173222541809</v>
+        <v>5.992067977786064</v>
       </c>
     </row>
     <row r="247">
@@ -6351,10 +6351,10 @@
         <v>299</v>
       </c>
       <c r="F257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G257" t="n">
-        <v>77.39623188972473</v>
+        <v>1.971420273184776</v>
       </c>
     </row>
     <row r="258">
@@ -6627,10 +6627,10 @@
         <v>312</v>
       </c>
       <c r="F269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>83.61008763313293</v>
+        <v>7.75148868560791</v>
       </c>
     </row>
     <row r="270">
@@ -6719,10 +6719,10 @@
         <v>299</v>
       </c>
       <c r="F273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G273" t="n">
-        <v>79.2289674282074</v>
+        <v>5.179375410079956</v>
       </c>
     </row>
     <row r="274">
@@ -6742,10 +6742,10 @@
         <v>309</v>
       </c>
       <c r="F274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G274" t="n">
-        <v>84.86546277999878</v>
+        <v>8.50636214017868</v>
       </c>
     </row>
     <row r="275">
@@ -6949,10 +6949,10 @@
         <v>299</v>
       </c>
       <c r="F283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G283" t="n">
-        <v>81.65546655654907</v>
+        <v>5.144748464226723</v>
       </c>
     </row>
     <row r="284">
@@ -7432,10 +7432,10 @@
         <v>316</v>
       </c>
       <c r="F304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G304" t="n">
-        <v>87.25769519805908</v>
+        <v>11.04656606912613</v>
       </c>
     </row>
     <row r="305">
@@ -7869,10 +7869,10 @@
         <v>318</v>
       </c>
       <c r="F323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>86.19786500930786</v>
+        <v>9.930257499217987</v>
       </c>
     </row>
     <row r="324">
@@ -8076,10 +8076,10 @@
         <v>307</v>
       </c>
       <c r="F332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>82.19714164733887</v>
+        <v>5.434873700141907</v>
       </c>
     </row>
     <row r="333">
@@ -9157,10 +9157,10 @@
         <v>311</v>
       </c>
       <c r="F379" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G379" t="n">
-        <v>81.96420073509216</v>
+        <v>6.188629940152168</v>
       </c>
     </row>
     <row r="380">
@@ -9663,10 +9663,10 @@
         <v>305</v>
       </c>
       <c r="F401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>77.71723866462708</v>
+        <v>2.388804219663143</v>
       </c>
     </row>
     <row r="402">
@@ -9732,10 +9732,10 @@
         <v>317</v>
       </c>
       <c r="F404" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>83.24782848358154</v>
+        <v>9.217682480812073</v>
       </c>
     </row>
     <row r="405">
@@ -10261,10 +10261,10 @@
         <v>299</v>
       </c>
       <c r="F427" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G427" t="n">
-        <v>74.31372404098511</v>
+        <v>1.473205164074898</v>
       </c>
     </row>
     <row r="428">
@@ -10583,10 +10583,10 @@
         <v>318</v>
       </c>
       <c r="F441" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G441" t="n">
-        <v>81.47448897361755</v>
+        <v>7.523472607135773</v>
       </c>
     </row>
     <row r="442">
@@ -10721,10 +10721,10 @@
         <v>315</v>
       </c>
       <c r="F447" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G447" t="n">
-        <v>77.6801586151123</v>
+        <v>3.540847077965736</v>
       </c>
     </row>
     <row r="448">
@@ -11020,10 +11020,10 @@
         <v>304</v>
       </c>
       <c r="F460" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G460" t="n">
-        <v>84.92861390113831</v>
+        <v>7.339709252119064</v>
       </c>
     </row>
     <row r="461">
@@ -11135,10 +11135,10 @@
         <v>318</v>
       </c>
       <c r="F465" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G465" t="n">
-        <v>80.5503785610199</v>
+        <v>5.353875458240509</v>
       </c>
     </row>
     <row r="466">
@@ -11411,10 +11411,10 @@
         <v>300</v>
       </c>
       <c r="F477" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G477" t="n">
-        <v>80.45380711555481</v>
+        <v>5.39892166852951</v>
       </c>
     </row>
     <row r="478">
@@ -11572,10 +11572,10 @@
         <v>318</v>
       </c>
       <c r="F484" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G484" t="n">
-        <v>81.76440000534058</v>
+        <v>6.604047119617462</v>
       </c>
     </row>
     <row r="485">
@@ -11710,10 +11710,10 @@
         <v>300</v>
       </c>
       <c r="F490" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G490" t="n">
-        <v>75.50781965255737</v>
+        <v>2.106846868991852</v>
       </c>
     </row>
     <row r="491">
@@ -11825,10 +11825,10 @@
         <v>302</v>
       </c>
       <c r="F495" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G495" t="n">
-        <v>78.59719395637512</v>
+        <v>3.793703019618988</v>
       </c>
     </row>
     <row r="496">
@@ -12032,10 +12032,10 @@
         <v>312</v>
       </c>
       <c r="F504" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G504" t="n">
-        <v>82.02536702156067</v>
+        <v>7.137896120548248</v>
       </c>
     </row>
     <row r="505">
@@ -12860,10 +12860,10 @@
         <v>305</v>
       </c>
       <c r="F540" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G540" t="n">
-        <v>79.7381579875946</v>
+        <v>4.571729153394699</v>
       </c>
     </row>
     <row r="541">
@@ -12906,10 +12906,10 @@
         <v>306</v>
       </c>
       <c r="F542" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G542" t="n">
-        <v>72.01590538024902</v>
+        <v>0.3303081262856722</v>
       </c>
     </row>
     <row r="543">
@@ -12929,10 +12929,10 @@
         <v>313</v>
       </c>
       <c r="F543" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G543" t="n">
-        <v>86.94501519203186</v>
+        <v>10.71618795394897</v>
       </c>
     </row>
     <row r="544">
@@ -13044,10 +13044,10 @@
         <v>301</v>
       </c>
       <c r="F548" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G548" t="n">
-        <v>77.33671069145203</v>
+        <v>3.199740126729012</v>
       </c>
     </row>
     <row r="549">
@@ -13113,10 +13113,10 @@
         <v>309</v>
       </c>
       <c r="F551" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G551" t="n">
-        <v>82.79107213020325</v>
+        <v>6.788725405931473</v>
       </c>
     </row>
     <row r="552">
@@ -13527,10 +13527,10 @@
         <v>307</v>
       </c>
       <c r="F569" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G569" t="n">
-        <v>76.49332880973816</v>
+        <v>1.947877369821072</v>
       </c>
     </row>
     <row r="570">
@@ -13596,10 +13596,10 @@
         <v>317</v>
       </c>
       <c r="F572" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G572" t="n">
-        <v>85.73373556137085</v>
+        <v>9.668522328138351</v>
       </c>
     </row>
     <row r="573">
@@ -13780,10 +13780,10 @@
         <v>315</v>
       </c>
       <c r="F580" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G580" t="n">
-        <v>87.85431981086731</v>
+        <v>10.32558903098106</v>
       </c>
     </row>
     <row r="581">
@@ -13803,10 +13803,10 @@
         <v>307</v>
       </c>
       <c r="F581" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G581" t="n">
-        <v>79.83521819114685</v>
+        <v>4.443135857582092</v>
       </c>
     </row>
     <row r="582">
@@ -14056,10 +14056,10 @@
         <v>307</v>
       </c>
       <c r="F592" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G592" t="n">
-        <v>79.93636727333069</v>
+        <v>4.64046522974968</v>
       </c>
     </row>
     <row r="593">
@@ -14148,10 +14148,10 @@
         <v>309</v>
       </c>
       <c r="F596" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G596" t="n">
-        <v>72.32773303985596</v>
+        <v>0.1289988402277231</v>
       </c>
     </row>
     <row r="597">
@@ -14194,10 +14194,10 @@
         <v>319</v>
       </c>
       <c r="F598" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G598" t="n">
-        <v>86.32243871688843</v>
+        <v>10.54178178310394</v>
       </c>
     </row>
     <row r="599">
@@ -14263,10 +14263,10 @@
         <v>310</v>
       </c>
       <c r="F601" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G601" t="n">
-        <v>81.91580176353455</v>
+        <v>6.042813137173653</v>
       </c>
     </row>
     <row r="602">
@@ -14654,10 +14654,10 @@
         <v>314</v>
       </c>
       <c r="F618" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G618" t="n">
-        <v>87.34009861946106</v>
+        <v>10.97100153565407</v>
       </c>
     </row>
     <row r="619">
@@ -14907,10 +14907,10 @@
         <v>313</v>
       </c>
       <c r="F629" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G629" t="n">
-        <v>82.57271647453308</v>
+        <v>6.731297820806503</v>
       </c>
     </row>
     <row r="630">
@@ -15091,10 +15091,10 @@
         <v>317</v>
       </c>
       <c r="F637" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G637" t="n">
-        <v>87.53889203071594</v>
+        <v>10.41108891367912</v>
       </c>
     </row>
     <row r="638">
@@ -15436,10 +15436,10 @@
         <v>308</v>
       </c>
       <c r="F652" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G652" t="n">
-        <v>81.67273998260498</v>
+        <v>5.125270783901215</v>
       </c>
     </row>
     <row r="653">
@@ -15482,10 +15482,10 @@
         <v>319</v>
       </c>
       <c r="F654" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G654" t="n">
-        <v>82.55574107170105</v>
+        <v>8.016190677881241</v>
       </c>
     </row>
     <row r="655">
@@ -15850,10 +15850,10 @@
         <v>318</v>
       </c>
       <c r="F670" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G670" t="n">
-        <v>79.94735836982727</v>
+        <v>6.529497355222702</v>
       </c>
     </row>
     <row r="671">
@@ -16379,10 +16379,10 @@
         <v>309</v>
       </c>
       <c r="F693" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G693" t="n">
-        <v>84.31011438369751</v>
+        <v>7.674072682857513</v>
       </c>
     </row>
     <row r="694">
@@ -16586,10 +16586,10 @@
         <v>312</v>
       </c>
       <c r="F702" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G702" t="n">
-        <v>80.04255890846252</v>
+        <v>5.242002755403519</v>
       </c>
     </row>
     <row r="703">
@@ -17184,10 +17184,10 @@
         <v>306</v>
       </c>
       <c r="F728" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G728" t="n">
-        <v>77.89883613586426</v>
+        <v>3.307235985994339</v>
       </c>
     </row>
     <row r="729">
@@ -17230,10 +17230,10 @@
         <v>312</v>
       </c>
       <c r="F730" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G730" t="n">
-        <v>83.03767442703247</v>
+        <v>7.4161097407341</v>
       </c>
     </row>
     <row r="731">
@@ -17322,10 +17322,10 @@
         <v>306</v>
       </c>
       <c r="F734" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G734" t="n">
-        <v>77.19314694404602</v>
+        <v>3.161738812923431</v>
       </c>
     </row>
     <row r="735">
